--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260617.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260617.xlsx
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>3,553,678</t>
+          <t>10,849,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>10,849,000</t>
+          <t>3,553,678</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>54,381,000</t>
+          <t>36,472,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>36,472,000</t>
+          <t>54,381,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
